--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,6 +594,116 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-01 21:27</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ed44aa2af31579c1076e7717eff93f36_1785619597.mp4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-01 21:29</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/68834782e159f4ca7179fa24964440b4_1785619724.mp4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep03/shots/shot_02.mp4</t>
         </is>
       </c>
     </row>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,116 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-02 21:33</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d1d2fbff822e77a0e310d9d57fdbfa93_1785705912.mp4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-02 21:35</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d2101f652b2209698d5cca2a3d2fc149_1785706489.mp4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep04/shots/shot_02.mp4</t>
         </is>
       </c>
     </row>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,6 +814,116 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-07 18:19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1d5d11833c96627b4f250b18768f76f9_1786126752.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-07 18:22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/492efd91c6264a21b6a6525fba60246b_1786126891.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep05/shots/shot_02.mp4</t>
         </is>
       </c>
     </row>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,6 +924,116 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-13 21:15</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2fd6d219ecd8b88112f31ed5963eb548_1786655681.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-13 21:20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3a023e8f247e95831a404fba4926e96b_1786655830.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep07/shots/shot_02.mp4</t>
         </is>
       </c>
     </row>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1037,116 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-14 20:57</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6b1a1363379c702290dd0526fedde2e6_1786741008.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ca1c46a88b93f131826a5c1744c66983_1786741205.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,116 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-15 20:50</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/07e1a7d6ad07678e433cf7635a2876a8_1786826848.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-15 20:53</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d90a005954adf9679faa4ccc155c3c89_1786827149.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep09/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,6 +1257,116 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-16 20:49</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2ab4d02008b9ece2b148aeeacd3111c9_1786913323.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-16 20:52</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/bb1cafdb2314e135939223704dd67f4e_1786913505.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep10/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1367,116 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-17 20:54</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f53989e6eaef24c14ee8facf0333ea40_1787000012.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep11/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-17 20:57</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0cebf02b2a9cf1d829e654bae98d4df3_1787000175.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep11/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,116 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:53</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/02933796770c96f3fcf67c103c2e4e6c_1787086367.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep12/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-18 21:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0286396161563e5af85015c3b33d7136_1787086564.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep12/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1587,6 +1587,116 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-19 21:26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/bb90ad8b3f898b199b8a62988b613140_1787174728.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep13/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-19 21:28</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/05e90f71baee6c5b614e0ae0275f1001_1787174862.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep13/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1697,6 +1697,116 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-20 20:57</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/530ef74316782ee5483685d162c8d4d2_1787259398.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep14/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-20 21:06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/264ac83ed4e790c86d8db48d5ce02ee8_1787259619.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep14/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1807,6 +1807,116 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-21 20:55</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/772b53d34eb7bea205830e74f3fff36c_1787345538.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep15/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-21 21:03</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5f6230816931caf2596255054b721618_1787345847.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep15/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1917,6 +1917,116 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-22 20:51</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/90100021fc3787bde03e01679aed879f_1787431830.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep16/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-22 20:54</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/71138d1985a8cef6d9f1c41912610471_1787432008.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep16/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2027,6 +2027,116 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:48</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d445e245d9ef20418b93a764f420794f_1787518089.mp4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep17/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-23 20:50</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6279c749e8bd8c4217b61c44c2224afc_1787518204.mp4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep17/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2137,6 +2137,116 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:59</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f9541a6274cea1263ac31b057ba02c5e_1787605110.mp4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep18/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-24 21:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/93ac71c9d8f8a7cf621d845792791728_1787605227.mp4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep18/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2247,6 +2247,116 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-25 20:56</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/dd8b7201fe9a419e6e1567bfce8cf3db_1787691331.mp4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep19/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-25 20:58</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ea1022f0fe0247a8328e690f2012cf3c_1787691452.mp4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep19/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2357,6 +2357,116 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-27 00:04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/081cc21dc5b481582f9a47863f3a51ae_1787788860.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep20/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-27 00:08</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1c4682be502446e1e01b92b02f7f5c68_1787789180.mp4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep20/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2467,6 +2467,171 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-29 03:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ea2959ec285c04aaf711e9e666a534a1_1787972376.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep21/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-31 22:22</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8c41f92851e14af1737dcf2de38bb1c4_1788214685.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep21/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-31 22:24</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fbf2b02a83165ba6104b07d199e2e635_1788215024.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep21/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2632,6 +2632,116 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-01 22:46</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/654df400f1abd6a0028acf86096f610f_1788302652.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep22/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-01 22:49</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b06ed1800c865bdab4d6bee7e14cf57c_1788302917.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep22/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2742,6 +2742,116 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-02 22:49</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a478002288eca7c405b92601314d7e21_1788389207.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep23/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-02 22:51</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/73164c805f5b13f2ba2fa7fbcd8ab1e4_1788389443.mp4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep23/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2852,6 +2852,116 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-03 22:45</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d8e7496c557272fa58abc74c61058c2e_1788475477.mp4</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep24/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-03 22:49</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/15ebdd276676189e3a6337f62260b661_1788475601.mp4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep24/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2962,6 +2962,116 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:30</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7c57145ef90c41ad2bd910d58a560586_1788560957.mp4</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep25/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:34</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ecfdf01ea738693de8e854cef193b741_1788561091.mp4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep25/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3072,6 +3072,116 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:12</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/414d7babd8007a2a5f2d6bb415addc88_1788646214.mp4</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep26/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:17</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8c34543df3345563dc65b31e439fba10_1788646481.mp4</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep26/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3182,6 +3182,116 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f3003b3af9ed8bc6c846b27a989b16ae_1788732834.mp4</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep27/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:19</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/831c00f33402825a67215f664c130151_1788733119.mp4</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep27/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3292,6 +3292,116 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:58</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/30f9e3e775e40421e5b347c794915db7_1788821857.mp4</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep28/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-07 23:00</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/13cb81c1c95828aa1b9117256daa120c_1788822010.mp4</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep28/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3402,6 +3402,116 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-08 22:52</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b528587469053ed6a249f960789dc5dc_1788907939.mp4</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep29/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-08 22:55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/96b0ade282f6fa51f8afdfc39468dff0_1788908062.mp4</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep29/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/flashpoints/series_log.xlsx
+++ b/shadowedhistory/flashpoints/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3512,6 +3512,116 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-09 22:45</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3069b4882c468c10a27c63544e403f2f_1788993912.mp4</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep30/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-09 22:49</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d1c832458a66011fc04b05c4f4d8b1cc_1788994032.mp4</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/flashpoints/episodes/ep30/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
